--- a/erp-server/erp-server-file/src/main/resources/excel/tms/smallBagCostAllocation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/smallBagCostAllocation.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>核算</t>
   </si>
@@ -61,6 +59,9 @@
     <t>跟踪号</t>
   </si>
   <si>
+    <t>销售出库单平台订单号</t>
+  </si>
+  <si>
     <t>发货</t>
   </si>
   <si>
@@ -158,6 +159,9 @@
   </si>
   <si>
     <t>{.trackNo}</t>
+  </si>
+  <si>
+    <t>{.platformCode}</t>
   </si>
   <si>
     <t>{.deliveryTime}</t>
@@ -1163,7 +1167,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
@@ -1175,30 +1179,31 @@
     <col min="8" max="8" width="17.125" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="11" width="17.125" customWidth="1"/>
-    <col min="12" max="13" width="16.375" customWidth="1"/>
-    <col min="14" max="14" width="12.625" customWidth="1"/>
-    <col min="15" max="15" width="16.375" customWidth="1"/>
-    <col min="16" max="16" width="9.375" customWidth="1"/>
-    <col min="17" max="17" width="16.25" customWidth="1"/>
-    <col min="18" max="18" width="16" customWidth="1"/>
-    <col min="19" max="19" width="18.25" customWidth="1"/>
-    <col min="20" max="20" width="22.5" customWidth="1"/>
-    <col min="21" max="21" width="13.75" customWidth="1"/>
-    <col min="22" max="22" width="12.625" customWidth="1"/>
-    <col min="23" max="23" width="13.75" customWidth="1"/>
-    <col min="24" max="25" width="20.75" customWidth="1"/>
-    <col min="26" max="26" width="14.875" customWidth="1"/>
-    <col min="27" max="27" width="20.375" customWidth="1"/>
-    <col min="28" max="28" width="28.25" customWidth="1"/>
-    <col min="29" max="30" width="18.25" customWidth="1"/>
-    <col min="31" max="31" width="15.75" customWidth="1"/>
-    <col min="32" max="32" width="13.875" customWidth="1"/>
-    <col min="33" max="33" width="13.75" customWidth="1"/>
-    <col min="34" max="34" width="13.125" customWidth="1"/>
+    <col min="11" max="11" width="22.75" customWidth="1"/>
+    <col min="12" max="12" width="17.125" customWidth="1"/>
+    <col min="13" max="14" width="16.375" customWidth="1"/>
+    <col min="15" max="15" width="12.625" customWidth="1"/>
+    <col min="16" max="16" width="16.375" customWidth="1"/>
+    <col min="17" max="17" width="9.375" customWidth="1"/>
+    <col min="18" max="18" width="16.25" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="20" max="20" width="18.25" customWidth="1"/>
+    <col min="21" max="21" width="22.5" customWidth="1"/>
+    <col min="22" max="22" width="13.75" customWidth="1"/>
+    <col min="23" max="23" width="12.625" customWidth="1"/>
+    <col min="24" max="24" width="13.75" customWidth="1"/>
+    <col min="25" max="26" width="20.75" customWidth="1"/>
+    <col min="27" max="27" width="14.875" customWidth="1"/>
+    <col min="28" max="28" width="20.375" customWidth="1"/>
+    <col min="29" max="29" width="28.25" customWidth="1"/>
+    <col min="30" max="31" width="18.25" customWidth="1"/>
+    <col min="32" max="32" width="15.75" customWidth="1"/>
+    <col min="33" max="33" width="13.875" customWidth="1"/>
+    <col min="34" max="34" width="13.75" customWidth="1"/>
+    <col min="35" max="35" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1233,10 +1238,10 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
         <v>4</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
       </c>
       <c r="N1" t="s">
         <v>12</v>
@@ -1280,10 +1285,10 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
       <c r="AD1" t="s">
@@ -1301,109 +1306,115 @@
       <c r="AH1" t="s">
         <v>32</v>
       </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:35">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Y2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AC2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AD2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AE2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AF2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AG2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AH2" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1411,28 +1422,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-file/src/main/resources/excel/tms/smallBagCostAllocation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/smallBagCostAllocation.xlsx
@@ -59,7 +59,7 @@
     <t>跟踪号</t>
   </si>
   <si>
-    <t>销售出库单平台订单号</t>
+    <t>平台订单号</t>
   </si>
   <si>
     <t>发货</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/smallBagCostAllocation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/smallBagCostAllocation.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
   <si>
     <t>核算</t>
   </si>
@@ -74,6 +74,9 @@
     <t>国家</t>
   </si>
   <si>
+    <t>平台</t>
+  </si>
+  <si>
     <t>SKU</t>
   </si>
   <si>
@@ -177,6 +180,9 @@
   </si>
   <si>
     <t>{.toCountry}</t>
+  </si>
+  <si>
+    <t>{.salesPlatformName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -1167,7 +1173,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
@@ -1184,26 +1190,27 @@
     <col min="13" max="14" width="16.375" customWidth="1"/>
     <col min="15" max="15" width="12.625" customWidth="1"/>
     <col min="16" max="16" width="16.375" customWidth="1"/>
-    <col min="17" max="17" width="9.375" customWidth="1"/>
-    <col min="18" max="18" width="16.25" customWidth="1"/>
-    <col min="19" max="19" width="16" customWidth="1"/>
-    <col min="20" max="20" width="18.25" customWidth="1"/>
-    <col min="21" max="21" width="22.5" customWidth="1"/>
-    <col min="22" max="22" width="13.75" customWidth="1"/>
-    <col min="23" max="23" width="12.625" customWidth="1"/>
-    <col min="24" max="24" width="13.75" customWidth="1"/>
-    <col min="25" max="26" width="20.75" customWidth="1"/>
-    <col min="27" max="27" width="14.875" customWidth="1"/>
-    <col min="28" max="28" width="20.375" customWidth="1"/>
-    <col min="29" max="29" width="28.25" customWidth="1"/>
-    <col min="30" max="31" width="18.25" customWidth="1"/>
-    <col min="32" max="32" width="15.75" customWidth="1"/>
-    <col min="33" max="33" width="13.875" customWidth="1"/>
-    <col min="34" max="34" width="13.75" customWidth="1"/>
-    <col min="35" max="35" width="13.125" customWidth="1"/>
+    <col min="17" max="17" width="16.875" customWidth="1"/>
+    <col min="18" max="18" width="9.375" customWidth="1"/>
+    <col min="19" max="19" width="16.25" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="18.25" customWidth="1"/>
+    <col min="22" max="22" width="22.5" customWidth="1"/>
+    <col min="23" max="23" width="13.75" customWidth="1"/>
+    <col min="24" max="24" width="12.625" customWidth="1"/>
+    <col min="25" max="25" width="13.75" customWidth="1"/>
+    <col min="26" max="27" width="20.75" customWidth="1"/>
+    <col min="28" max="28" width="14.875" customWidth="1"/>
+    <col min="29" max="29" width="20.375" customWidth="1"/>
+    <col min="30" max="30" width="28.25" customWidth="1"/>
+    <col min="31" max="32" width="18.25" customWidth="1"/>
+    <col min="33" max="33" width="15.75" customWidth="1"/>
+    <col min="34" max="34" width="13.875" customWidth="1"/>
+    <col min="35" max="35" width="13.75" customWidth="1"/>
+    <col min="36" max="36" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:36">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1288,10 +1295,10 @@
       <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="AE1" t="s">
@@ -1309,112 +1316,118 @@
       <c r="AI1" t="s">
         <v>33</v>
       </c>
+      <c r="AJ1" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:36">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="X2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AB2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AC2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AD2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AF2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AH2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AI2" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
